--- a/Temp_118_Delta_S-N.xlsx
+++ b/Temp_118_Delta_S-N.xlsx
@@ -8,18 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19065963\Downloads\Emissions_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D264103-61C6-407B-B049-A3DFBEBD79E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083A907A-BA7A-44AF-A9A8-D7906DFE6A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-225" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$I$2:$I$77</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$J$2:$J$77</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,12 +36,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>Temp</t>
+    <t>D</t>
   </si>
   <si>
-    <t>Wet bulb</t>
+    <t>S1 Dry</t>
+  </si>
+  <si>
+    <t>S1 Wet</t>
+  </si>
+  <si>
+    <t>N Dry</t>
+  </si>
+  <si>
+    <t>N Wet</t>
+  </si>
+  <si>
+    <t>Delta Wet</t>
+  </si>
+  <si>
+    <t>Delta Dry</t>
+  </si>
+  <si>
+    <t>(Delta - D) Wet</t>
+  </si>
+  <si>
+    <t>(Delta - D) Dry</t>
+  </si>
+  <si>
+    <t>(S1 + Delta - D) Wet</t>
+  </si>
+  <si>
+    <t>(S1 + Delta - D) Dry</t>
   </si>
 </sst>
 </file>
@@ -137,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>114 Delta  </a:t>
+              <a:t>118 Delta  </a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -434,237 +456,237 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$2:$I$77</c:f>
+              <c:f>Sheet1!$H$2:$H$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>1.4000000000000004</c:v>
+                  <c:v>0.19999999999999929</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69999999999999929</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.60000000000000142</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5</c:v>
+                  <c:v>-0.19999999999999929</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29999999999999716</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.9999999999997868E-2</c:v>
+                  <c:v>0.19999999999999929</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-9.9999999999999645E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.10000000000000142</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>-0.10000000000000142</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.69999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.39999999999999858</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.19999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.30000000000000071</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.30000000000000071</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.59999999999999964</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="19">
+                  <c:v>1.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.4999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.7000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.5999999999999979</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4.4999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4.4999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.4000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.4000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4.0999999999999979</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.2000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.2999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.4999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.2999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4.7000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.2000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5.2000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.7000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>3.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.39999999999999858</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>0.60000000000000142</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.80000000000000071</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.59999999999999787</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>9.9999999999997868E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.3000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2.3000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2.6000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>4.8000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2.7999999999999989</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4.0999999999999996</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>4.8999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>5.4000000000000021</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>5.4000000000000021</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>5.4</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>5.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>5.2000000000000011</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>5.4</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>5.0999999999999996</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>5.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>5.1000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>5.1000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>5.0000000000000018</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>6.7999999999999989</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>5.8999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>7.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>7.8999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>9.1</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>7.7000000000000011</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>6.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>10.100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>9.8000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>9.8000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>9.7000000000000011</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>9.9</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>9.6</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>7.7000000000000011</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>7.5000000000000018</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>8.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>10.3</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>8.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>6.5999999999999979</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>7.8000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>9.3000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>9.4000000000000021</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>7.4000000000000021</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>7.1000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>8.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>9.1</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>10.100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>8.5000000000000018</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>7.8000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>8.1</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>7.5000000000000018</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>5.7000000000000011</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>5.7999999999999989</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>2.8000000000000007</c:v>
-                </c:pt>
                 <c:pt idx="75">
-                  <c:v>2.1999999999999993</c:v>
+                  <c:v>0.60000000000000142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -933,237 +955,237 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$2:$J$77</c:f>
+              <c:f>Sheet1!$I$2:$I$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="76"/>
                 <c:pt idx="0">
+                  <c:v>-0.80000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.89999999999999858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.80000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.30000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.30000000000000071</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.19999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.40000000000000213</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.69999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1.2999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.69999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.70000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.19999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.59999999999999787</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.39999999999999858</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.69999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.0999999999999979</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.7000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.4000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.4000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.89999999999999858</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.80000000000000071</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.70000000000000284</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="75">
                   <c:v>0.39999999999999858</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.30000000000000071</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-0.10000000000000142</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-0.10000000000000142</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.30000000000000071</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.0999999999999979</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.5999999999999979</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.4000000000000021</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.79999999999999716</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.2000000000000028</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1.3999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>3.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2.3999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>3.2000000000000028</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.8999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>4.3000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>4.6000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>4.6000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.6000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>4.3999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>7.3999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>9.2000000000000028</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>9.6000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>8.5</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>11.899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>11.899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>12.2</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>12.100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>12.399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>12.399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>9.6000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>8.8000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>12.2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>10.200000000000003</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>8.3999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>10.399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>11.100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>9.1000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>8.1000000000000014</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>10.100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>10.899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>14.100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>12.3</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>11.3</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>10.899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>9.8999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>9.1999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>6.3000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>6.3999999999999986</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>5.3000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>4.6000000000000014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1340,8 +1362,8 @@
         <c:axId val="1062795392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="15"/>
-          <c:min val="-1"/>
+          <c:max val="7"/>
+          <c:min val="-2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1585,7 +1607,2517 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$24:$H$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.7000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.5999999999999979</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.4999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.4999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.4000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.4000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.0999999999999979</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.2000000000000011</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6404-4F62-B92A-B631CC9BEB77}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$24:$I$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>3.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0999999999999979</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.7000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.4000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.8000000000000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6404-4F62-B92A-B631CC9BEB77}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="907768943"/>
+        <c:axId val="948450719"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="907768943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="948450719"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="948450719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="907768943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$47:$H$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>5.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.7999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.4999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.2999999999999989</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.7000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.9999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.2000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.2000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.7000000000000011</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4513-48F1-A27A-D7E6AE67543D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$47:$I$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>5.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4000000000000021</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.1000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.3999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.8999999999999986</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4513-48F1-A27A-D7E6AE67543D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1609812463"/>
+        <c:axId val="1609813423"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1609812463"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1609813423"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1609813423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1609812463"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>118 Delta - D</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Wet Bulb</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$77</c:f>
+              <c:numCache>
+                <c:formatCode>h:mm</c:formatCode>
+                <c:ptCount val="76"/>
+                <c:pt idx="0">
+                  <c:v>0.43402777777777779</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4375</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.44097222222222199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.44444444444444398</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.44791666666666702</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45138888888888901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.45486111111111099</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45833333333333298</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.46180555555555503</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.46527777777777801</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.46875</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.47222222222222199</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.47569444444444398</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.47916666666666702</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.48263888888888901</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.48611111111111099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.48958333333333298</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.49305555555555503</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.49652777777777801</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.50347222222222199</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.50694444444444398</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.51041666666666596</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.51388888888888895</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.51736111111111105</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.52083333333333304</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.52430555555555503</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.52777777777777701</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.53125</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.53472222222222199</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.53819444444444398</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.54166666666666696</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.54513888888888895</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.54861111111111105</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.55208333333333304</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.55555555555555503</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.55902777777777801</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.5625</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.56597222222222199</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.56944444444444398</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.57291666666666596</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.57638888888888895</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.57986111111111105</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.58333333333333304</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.58680555555555503</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.59027777777777701</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.59375</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.59722222222222199</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.60069444444444398</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.60416666666666596</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.60763888888888795</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.61111111111111105</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.61458333333333304</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.61805555555555503</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.62152777777777701</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.62847222222222199</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.63194444444444398</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.63541666666666596</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.63888888888888795</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.64236111111111105</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.64583333333333304</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.64930555555555503</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.65277777777777701</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.656249999999999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.65972222222222199</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.66319444444444398</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.66666666666666596</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.67013888888888795</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.67361111111111005</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.67708333333333304</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.68055555555555503</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.68402777777777701</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.687499999999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.69097222222222199</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.69444444444444398</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$K$2:$K$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="76"/>
+                <c:pt idx="0">
+                  <c:v>-4.3285714285714301</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.7285714285714286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.3285714285714301</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4.4285714285714279</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.6285714285714308</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5.0285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-3.8285714285714301</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-4.1285714285714308</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.2285714285714322</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-4.5285714285714294</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-4.3285714285714301</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-4.2285714285714286</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-2.6285714285714308</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.72857142857143042</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-1.0285714285714311</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.371428571428571</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.47142857142857064</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.27142857142856958</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.17142857142857171</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.1428571428570287E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.1428571428570287E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7.142857142856851E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-2.8571428571431134E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-2.8571428571431134E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.128571428571429</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.4714285714285689</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.371428571428571</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.17142857142856993</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-2.8571428571429358E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.128571428571429</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.52857142857143113</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.72857142857142865</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.52857142857143113</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.628571428571429</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.42857142857143149</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.32857142857142829</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.371428571428571</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.871428571428571</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.2714285714285696</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.77142857142856958</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.871428571428571</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.2714285714285696</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.97142857142856887</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.67142857142856993</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.1714285714285699</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.9714285714285706</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.9714285714285706</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.2714285714285714</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.77142857142856958</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.17142857142857171</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.47142857142856887</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.0714285714285721</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.67142857142856993</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.47142857142857064</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.67142857142857171</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.0714285714285721</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.2714285714285714</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.871428571428571</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.67142857142857171</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.371428571428571</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.17142857142856993</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.57142857142857206</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.17142857142857171</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.371428571428571</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.871428571428571</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-1.1285714285714308</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-4.1285714285714308</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-3.9285714285714279</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>-3.9285714285714279</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8AAC-4602-89A8-7934720D00AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Dry Bulb</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$77</c:f>
+              <c:numCache>
+                <c:formatCode>h:mm</c:formatCode>
+                <c:ptCount val="76"/>
+                <c:pt idx="0">
+                  <c:v>0.43402777777777779</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4375</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.44097222222222199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.44444444444444398</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.44791666666666702</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45138888888888901</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.45486111111111099</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45833333333333298</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.46180555555555503</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.46527777777777801</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.46875</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.47222222222222199</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.47569444444444398</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.47916666666666702</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.48263888888888901</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.48611111111111099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.48958333333333298</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.49305555555555503</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.49652777777777801</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.50347222222222199</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.50694444444444398</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.51041666666666596</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.51388888888888895</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.51736111111111105</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.52083333333333304</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.52430555555555503</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.52777777777777701</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.53125</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.53472222222222199</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.53819444444444398</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.54166666666666696</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.54513888888888895</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.54861111111111105</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.55208333333333304</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.55555555555555503</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.55902777777777801</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.5625</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.56597222222222199</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.56944444444444398</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.57291666666666596</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.57638888888888895</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.57986111111111105</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.58333333333333304</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.58680555555555503</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.59027777777777701</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.59375</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.59722222222222199</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.60069444444444398</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.60416666666666596</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.60763888888888795</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.61111111111111105</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.61458333333333304</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.61805555555555503</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.62152777777777701</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.62847222222222199</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.63194444444444398</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.63541666666666596</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.63888888888888795</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.64236111111111105</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.64583333333333304</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.64930555555555503</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.65277777777777701</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.656249999999999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.65972222222222199</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.66319444444444398</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.66666666666666596</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.67013888888888795</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.67361111111111005</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.67708333333333304</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.68055555555555503</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.68402777777777701</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.687499999999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.69097222222222199</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.69444444444444398</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$L$2:$L$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="76"/>
+                <c:pt idx="0">
+                  <c:v>-4.9428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.0428571428571409</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.9428571428571395</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.9428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.6428571428571423</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.4428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.4428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4.3428571428571416</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.5428571428571445</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.8428571428571416</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5.1428571428571423</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5.4428571428571395</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-4.8428571428571416</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-4.8428571428571452</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.3428571428571416</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-4.6428571428571423</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-4.7428571428571402</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-4.5428571428571409</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-4.4428571428571395</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-3.4428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-1.9428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.84285714285714164</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.24285714285714377</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-4.2857142857144481E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.714285714285694E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-4.2857142857140929E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-4.2857142857140929E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-4.2857142857140929E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-4.2857142857140929E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.14285714285714235</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.24285714285714377</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.24285714285714377</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.5571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.75714285714285623</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.55714285714286049</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.25714285714285978</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>5.714285714285694E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.34285714285714164</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.34285714285714164</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.34285714285714164</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.44285714285714306</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.34285714285714164</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.34285714285714164</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.35714285714285765</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.0571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.6571428571428584</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.3571428571428577</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.3571428571428577</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.7571428571428562</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.4571428571428591</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.2571428571428598</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.2571428571428562</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.0571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.1571428571428584</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.8571428571428577</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.4571428571428591</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.75714285714285623</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.85714285714285765</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.5571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2571428571428562</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.0571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.95714285714285907</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.3571428571428577</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.5571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1.2571428571428562</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.0571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.65714285714285836</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.35714285714285765</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.75714285714285623</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.75714285714285623</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.85714285714285765</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1.2571428571428562</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.15714285714285836</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-1.9428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-3.1428571428571423</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>-3.7428571428571438</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8AAC-4602-89A8-7934720D00AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="286623151"/>
+        <c:axId val="286624591"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="286623151"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Time (24-hour format)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.42277182257405671"/>
+              <c:y val="0.82602927417440952"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="h:mm" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="286624591"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="286624591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
+                    <a:solidFill>
+                      <a:prstClr val="black">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:prstClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Temperature </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>(˚C)</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0" dirty="0">
+                    <a:solidFill>
+                      <a:prstClr val="black">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:prstClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="286623151"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.33805304748355469"/>
+          <c:y val="0.89628510489725111"/>
+          <c:w val="0.26704511493585426"/>
+          <c:h val="6.5123475828857094E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2141,19 +4673,1567 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>152401</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>371476</xdr:colOff>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2174,6 +6254,114 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>166687</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>385762</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91EDEA8F-250D-9B31-722E-BB770393E668}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>442912</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>138112</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ACFE9B2-67FA-D187-FC63-8788921698E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>266699</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C076ACBD-57A2-86B0-316A-A0328117C9B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2445,174 +6633,301 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
       <c r="I1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" t="s">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0.43402777777777779</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2">
-        <v>20.5</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="D2">
-        <v>17.3</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
       <c r="F2">
-        <v>15.9</v>
+        <v>15.8</v>
+      </c>
+      <c r="H2">
+        <f>D2-F2</f>
+        <v>0.19999999999999929</v>
       </c>
       <c r="I2">
-        <f>D2-F2</f>
-        <v>1.4000000000000004</v>
-      </c>
-      <c r="J2">
         <f>C2-E2</f>
-        <v>1</v>
+        <v>-0.80000000000000071</v>
+      </c>
+      <c r="K2">
+        <f>H2-H$80</f>
+        <v>-4.3285714285714301</v>
+      </c>
+      <c r="L2">
+        <f>I2-I$80</f>
+        <v>-4.9428571428571431</v>
+      </c>
+      <c r="N2">
+        <f>D2+K2</f>
+        <v>11.671428571428571</v>
+      </c>
+      <c r="O2">
+        <f>C2+L2</f>
+        <v>14.457142857142856</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>0.4375</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3">
-        <v>20.9</v>
+        <v>19.8</v>
       </c>
       <c r="D3">
-        <v>16.7</v>
+        <v>15.8</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>15.8</v>
+      </c>
+      <c r="H3">
+        <f>D3-F3</f>
+        <v>0</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I66" si="0">D3-F3</f>
-        <v>0.69999999999999929</v>
-      </c>
-      <c r="J3">
         <f>C3-E3</f>
-        <v>0.89999999999999858</v>
+        <v>-0.89999999999999858</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="0">H3-H$80</f>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L66" si="1">I3-I$80</f>
+        <v>-5.0428571428571409</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N66" si="2">D3+K3</f>
+        <v>11.271428571428572</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O66" si="3">C3+L3</f>
+        <v>14.75714285714286</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>0.44097222222222199</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4">
-        <v>21</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="D4">
-        <v>16.600000000000001</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>20.2</v>
+        <v>20.9</v>
       </c>
       <c r="F4">
         <v>16</v>
       </c>
+      <c r="H4">
+        <f>D4-F4</f>
+        <v>0</v>
+      </c>
       <c r="I4">
+        <f>C4-E4</f>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.60000000000000142</v>
-      </c>
-      <c r="J4">
-        <f>C4-E4</f>
-        <v>0.80000000000000071</v>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="1"/>
+        <v>-4.9428571428571395</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="2"/>
+        <v>11.471428571428572</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="3"/>
+        <v>15.157142857142862</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>0.44444444444444398</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5">
+        <v>20.3</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
         <v>21.1</v>
       </c>
-      <c r="D5">
-        <v>16.5</v>
-      </c>
-      <c r="E5">
-        <v>20.399999999999999</v>
-      </c>
       <c r="F5">
-        <v>16</v>
+        <v>16.2</v>
+      </c>
+      <c r="H5">
+        <f>D5-F5</f>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="I5">
+        <f>C5-E5</f>
+        <v>-0.80000000000000071</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J5">
-        <f>C5-E5</f>
-        <v>0.70000000000000284</v>
+        <v>-4.7285714285714286</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="1"/>
+        <v>-4.9428571428571431</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="2"/>
+        <v>11.271428571428572</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="3"/>
+        <v>15.357142857142858</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>0.44791666666666702</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6">
-        <v>21</v>
+        <v>20.3</v>
       </c>
       <c r="D6">
-        <v>16.399999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="E6">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="F6">
-        <v>16.100000000000001</v>
+        <v>15.9</v>
+      </c>
+      <c r="H6">
+        <f>D6-F6</f>
+        <v>0</v>
       </c>
       <c r="I6">
+        <f>C6-E6</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.29999999999999716</v>
-      </c>
-      <c r="J6">
-        <f>C6-E6</f>
-        <v>0.39999999999999858</v>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>-4.6428571428571423</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="2"/>
+        <v>11.37142857142857</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="3"/>
+        <v>15.657142857142858</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>0.45138888888888901</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7">
-        <v>20.8</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="D7">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="F7">
-        <v>16.100000000000001</v>
+        <v>15.8</v>
+      </c>
+      <c r="H7">
+        <f>D7-F7</f>
+        <v>0.19999999999999929</v>
       </c>
       <c r="I7">
+        <f>C7-E7</f>
+        <v>-0.30000000000000071</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="0"/>
-        <v>9.9999999999997868E-2</v>
-      </c>
-      <c r="J7">
-        <f>C7-E7</f>
-        <v>0.30000000000000071</v>
+        <v>-4.3285714285714301</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="1"/>
+        <v>-4.4428571428571431</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="2"/>
+        <v>11.671428571428571</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="3"/>
+        <v>15.957142857142856</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>0.45486111111111099</v>
       </c>
@@ -2621,1815 +6936,2948 @@
         <v>20.2</v>
       </c>
       <c r="D8">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="E8">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>15.8</v>
+      </c>
+      <c r="H8">
+        <f>D8-F8</f>
+        <v>0</v>
       </c>
       <c r="I8">
+        <f>C8-E8</f>
+        <v>-0.30000000000000071</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="0"/>
-        <v>-9.9999999999999645E-2</v>
-      </c>
-      <c r="J8">
-        <f>C8-E8</f>
-        <v>-0.10000000000000142</v>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>-4.4428571428571431</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="2"/>
+        <v>11.271428571428572</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="3"/>
+        <v>15.757142857142856</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>0.45833333333333298</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9">
-        <v>19.899999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="D9">
         <v>15.8</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="F9">
         <v>15.7</v>
       </c>
+      <c r="H9">
+        <f>D9-F9</f>
+        <v>0.10000000000000142</v>
+      </c>
       <c r="I9">
+        <f>C9-E9</f>
+        <v>-0.19999999999999929</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="0"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="J9">
-        <f>C9-E9</f>
-        <v>-0.10000000000000142</v>
+        <v>-4.4285714285714279</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>-4.3428571428571416</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="2"/>
+        <v>11.371428571428574</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="3"/>
+        <v>15.857142857142858</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>0.46180555555555503</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10">
-        <v>20.100000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="D10">
         <v>16</v>
       </c>
       <c r="E10">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="F10">
-        <v>15.7</v>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="H10">
+        <f>D10-F10</f>
+        <v>-0.10000000000000142</v>
       </c>
       <c r="I10">
+        <f>C10-E10</f>
+        <v>-0.40000000000000213</v>
+      </c>
+      <c r="K10">
         <f t="shared" si="0"/>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="J10">
-        <f>C10-E10</f>
-        <v>0.30000000000000071</v>
+        <v>-4.6285714285714308</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>-4.5428571428571445</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="2"/>
+        <v>11.37142857142857</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="3"/>
+        <v>15.657142857142855</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>0.46527777777777801</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11">
-        <v>20.399999999999999</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="D11">
-        <v>16.100000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="E11">
-        <v>19.899999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="F11">
         <v>15.8</v>
       </c>
+      <c r="H11">
+        <f>D11-F11</f>
+        <v>0</v>
+      </c>
       <c r="I11">
+        <f>C11-E11</f>
+        <v>-0.69999999999999929</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="0"/>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="J11">
-        <f>C11-E11</f>
-        <v>0.5</v>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>-4.8428571428571416</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="2"/>
+        <v>11.271428571428572</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="3"/>
+        <v>15.25714285714286</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>0.46875</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12">
-        <v>20.7</v>
+        <v>19.8</v>
       </c>
       <c r="D12">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="E12">
-        <v>19.600000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="F12">
         <v>15.6</v>
       </c>
+      <c r="H12">
+        <f>D12-F12</f>
+        <v>0</v>
+      </c>
       <c r="I12">
+        <f>C12-E12</f>
+        <v>-1</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="0"/>
-        <v>0.59999999999999964</v>
-      </c>
-      <c r="J12">
-        <f>C12-E12</f>
-        <v>1.0999999999999979</v>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>-5.1428571428571423</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="2"/>
+        <v>11.071428571428569</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="3"/>
+        <v>14.657142857142858</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>0.47222222222222199</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13">
-        <v>21.2</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="D13">
-        <v>16.8</v>
+        <v>15.7</v>
       </c>
       <c r="E13">
-        <v>19.7</v>
+        <v>20.9</v>
       </c>
       <c r="F13">
         <v>16.2</v>
       </c>
+      <c r="H13">
+        <f>D13-F13</f>
+        <v>-0.5</v>
+      </c>
       <c r="I13">
+        <f>C13-E13</f>
+        <v>-1.2999999999999972</v>
+      </c>
+      <c r="K13">
         <f t="shared" si="0"/>
-        <v>0.60000000000000142</v>
-      </c>
-      <c r="J13">
-        <f>C13-E13</f>
-        <v>1.5</v>
+        <v>-5.0285714285714294</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>-5.4428571428571395</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="2"/>
+        <v>10.671428571428571</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="3"/>
+        <v>14.157142857142862</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>0.47569444444444398</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14">
-        <v>21.4</v>
+        <v>20.2</v>
       </c>
       <c r="D14">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="E14">
-        <v>19.8</v>
+        <v>20.9</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>16.3</v>
+      </c>
+      <c r="H14">
+        <f>D14-F14</f>
+        <v>0.69999999999999929</v>
       </c>
       <c r="I14">
+        <f>C14-E14</f>
+        <v>-0.69999999999999929</v>
+      </c>
+      <c r="K14">
         <f t="shared" si="0"/>
-        <v>0.80000000000000071</v>
-      </c>
-      <c r="J14">
-        <f>C14-E14</f>
-        <v>1.5999999999999979</v>
+        <v>-3.8285714285714301</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>-4.8428571428571416</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="2"/>
+        <v>13.171428571428571</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="3"/>
+        <v>15.357142857142858</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>0.47916666666666702</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15">
-        <v>21.3</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="D15">
         <v>16.7</v>
       </c>
       <c r="E15">
-        <v>19.899999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="F15">
-        <v>16.100000000000001</v>
+        <v>16.3</v>
+      </c>
+      <c r="H15">
+        <f>D15-F15</f>
+        <v>0.39999999999999858</v>
       </c>
       <c r="I15">
+        <f>C15-E15</f>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="K15">
         <f t="shared" si="0"/>
-        <v>0.59999999999999787</v>
-      </c>
-      <c r="J15">
-        <f>C15-E15</f>
-        <v>1.4000000000000021</v>
+        <v>-4.1285714285714308</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>-4.8428571428571452</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>12.571428571428569</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="3"/>
+        <v>15.557142857142853</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>0.48263888888888901</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="D16">
         <v>16.899999999999999</v>
       </c>
       <c r="E16">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="F16">
-        <v>16.8</v>
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H16">
+        <f>D16-F16</f>
+        <v>0.29999999999999716</v>
       </c>
       <c r="I16">
+        <f>C16-E16</f>
+        <v>-0.19999999999999929</v>
+      </c>
+      <c r="K16">
         <f t="shared" si="0"/>
-        <v>9.9999999999997868E-2</v>
-      </c>
-      <c r="J16">
-        <f>C16-E16</f>
-        <v>0.79999999999999716</v>
+        <v>-4.2285714285714322</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>-4.3428571428571416</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="2"/>
+        <v>12.671428571428567</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="3"/>
+        <v>16.75714285714286</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>0.48611111111111099</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="D17">
-        <v>18.100000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="E17">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="F17">
         <v>16.8</v>
       </c>
+      <c r="H17">
+        <f>D17-F17</f>
+        <v>0</v>
+      </c>
       <c r="I17">
+        <f>C17-E17</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K17">
         <f t="shared" si="0"/>
-        <v>1.3000000000000007</v>
-      </c>
-      <c r="J17">
-        <f>C17-E17</f>
-        <v>1</v>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>-4.6428571428571423</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="2"/>
+        <v>12.271428571428572</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="3"/>
+        <v>16.557142857142857</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>0.48958333333333298</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="D18">
-        <v>18.5</v>
+        <v>16.8</v>
       </c>
       <c r="E18">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="F18">
         <v>16.8</v>
       </c>
+      <c r="H18">
+        <f>D18-F18</f>
+        <v>0</v>
+      </c>
       <c r="I18">
+        <f>C18-E18</f>
+        <v>-0.59999999999999787</v>
+      </c>
+      <c r="K18">
         <f t="shared" si="0"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="J18">
-        <f>C18-E18</f>
-        <v>1.1999999999999993</v>
+        <v>-4.5285714285714294</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>-4.7428571428571402</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="2"/>
+        <v>12.271428571428572</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="3"/>
+        <v>16.357142857142861</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>0.49305555555555503</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19">
-        <v>22.5</v>
+        <v>21.1</v>
       </c>
       <c r="D19">
-        <v>18.399999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="E19">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="F19">
-        <v>16.7</v>
+        <v>16.600000000000001</v>
+      </c>
+      <c r="H19">
+        <f>D19-F19</f>
+        <v>0.19999999999999929</v>
       </c>
       <c r="I19">
+        <f>C19-E19</f>
+        <v>-0.39999999999999858</v>
+      </c>
+      <c r="K19">
         <f t="shared" si="0"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="J19">
-        <f>C19-E19</f>
-        <v>1.1999999999999993</v>
+        <v>-4.3285714285714301</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>-4.5428571428571409</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="2"/>
+        <v>12.471428571428572</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="3"/>
+        <v>16.55714285714286</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>0.49652777777777801</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20">
-        <v>22.6</v>
+        <v>21.1</v>
       </c>
       <c r="D20">
-        <v>18.5</v>
+        <v>16.8</v>
       </c>
       <c r="E20">
         <v>21.4</v>
       </c>
       <c r="F20">
-        <v>16.8</v>
+        <v>16.5</v>
+      </c>
+      <c r="H20">
+        <f>D20-F20</f>
+        <v>0.30000000000000071</v>
       </c>
       <c r="I20">
+        <f>C20-E20</f>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="K20">
         <f t="shared" si="0"/>
-        <v>1.6999999999999993</v>
-      </c>
-      <c r="J20">
-        <f>C20-E20</f>
-        <v>1.2000000000000028</v>
+        <v>-4.2285714285714286</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>-4.4428571428571395</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="2"/>
+        <v>12.571428571428573</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="3"/>
+        <v>16.657142857142862</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>0.5</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21">
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="D21">
-        <v>18.100000000000001</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E21">
-        <v>21.1</v>
+        <v>20.5</v>
       </c>
       <c r="F21">
-        <v>15.8</v>
+        <v>15</v>
+      </c>
+      <c r="H21">
+        <f>D21-F21</f>
+        <v>1.8999999999999986</v>
       </c>
       <c r="I21">
+        <f>C21-E21</f>
+        <v>0.69999999999999929</v>
+      </c>
+      <c r="K21">
         <f t="shared" si="0"/>
-        <v>2.3000000000000007</v>
-      </c>
-      <c r="J21">
-        <f>C21-E21</f>
-        <v>1.3999999999999986</v>
+        <v>-2.6285714285714308</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>-3.4428571428571431</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="2"/>
+        <v>14.271428571428569</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="3"/>
+        <v>17.757142857142856</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>0.50347222222222199</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22">
-        <v>22.5</v>
+        <v>21.3</v>
       </c>
       <c r="D22">
-        <v>18.3</v>
+        <v>17.2</v>
       </c>
       <c r="E22">
-        <v>20.8</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="F22">
-        <v>15.7</v>
+        <v>13.4</v>
+      </c>
+      <c r="H22">
+        <f>D22-F22</f>
+        <v>3.7999999999999989</v>
       </c>
       <c r="I22">
+        <f>C22-E22</f>
+        <v>2.1999999999999993</v>
+      </c>
+      <c r="K22">
         <f t="shared" si="0"/>
-        <v>2.6000000000000014</v>
-      </c>
-      <c r="J22">
-        <f>C22-E22</f>
-        <v>1.6999999999999993</v>
+        <v>-0.72857142857143042</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>-1.9428571428571431</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="2"/>
+        <v>16.471428571428568</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="3"/>
+        <v>19.357142857142858</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>0.50694444444444398</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23">
-        <v>22.4</v>
+        <v>21.2</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E23">
-        <v>19.2</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="F23">
-        <v>13.2</v>
+        <v>13.4</v>
+      </c>
+      <c r="H23">
+        <f>D23-F23</f>
+        <v>3.4999999999999982</v>
       </c>
       <c r="I23">
+        <f>C23-E23</f>
+        <v>3.3000000000000007</v>
+      </c>
+      <c r="K23">
         <f t="shared" si="0"/>
-        <v>4.8000000000000007</v>
-      </c>
-      <c r="J23">
-        <f>C23-E23</f>
-        <v>3.1999999999999993</v>
+        <v>-1.0285714285714311</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>-0.84285714285714164</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="2"/>
+        <v>15.871428571428567</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="3"/>
+        <v>20.357142857142858</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>0.51041666666666596</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24">
-        <v>22</v>
+        <v>21.2</v>
       </c>
       <c r="D24">
-        <v>17.399999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="E24">
-        <v>19.600000000000001</v>
+        <v>17.3</v>
       </c>
       <c r="F24">
-        <v>14.6</v>
+        <v>12.4</v>
+      </c>
+      <c r="H24">
+        <f>D24-F24</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I24">
+        <f>C24-E24</f>
+        <v>3.8999999999999986</v>
+      </c>
+      <c r="K24">
         <f t="shared" si="0"/>
-        <v>2.7999999999999989</v>
-      </c>
-      <c r="J24">
-        <f>C24-E24</f>
-        <v>2.3999999999999986</v>
+        <v>0.371428571428571</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>-0.24285714285714377</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="2"/>
+        <v>17.671428571428571</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="3"/>
+        <v>20.957142857142856</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>0.51388888888888895</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25">
-        <v>22.3</v>
+        <v>21.2</v>
       </c>
       <c r="D25">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="E25">
-        <v>19.3</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="F25">
-        <v>14</v>
+        <v>12.3</v>
+      </c>
+      <c r="H25">
+        <f>D25-F25</f>
+        <v>5</v>
       </c>
       <c r="I25">
+        <f>C25-E25</f>
+        <v>4.0999999999999979</v>
+      </c>
+      <c r="K25">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="J25">
-        <f>C25-E25</f>
-        <v>3</v>
+        <v>0.47142857142857064</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>-4.2857142857144481E-2</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="2"/>
+        <v>17.771428571428572</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="3"/>
+        <v>21.157142857142855</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>0.51736111111111105</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="D26">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="E26">
-        <v>18.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="F26">
-        <v>13.9</v>
+        <v>12.4</v>
+      </c>
+      <c r="H26">
+        <f>D26-F26</f>
+        <v>4.7999999999999989</v>
       </c>
       <c r="I26">
+        <f>C26-E26</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="K26">
         <f t="shared" si="0"/>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J26">
-        <f>C26-E26</f>
-        <v>3.2000000000000028</v>
+        <v>0.27142857142856958</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>5.714285714285694E-2</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="2"/>
+        <v>17.471428571428568</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="3"/>
+        <v>21.257142857142856</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>0.52083333333333304</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="D27">
-        <v>18.399999999999999</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="E27">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="F27">
-        <v>13.5</v>
+        <v>12.4</v>
+      </c>
+      <c r="H27">
+        <f>D27-F27</f>
+        <v>4.7000000000000011</v>
       </c>
       <c r="I27">
+        <f>C27-E27</f>
+        <v>4.1000000000000014</v>
+      </c>
+      <c r="K27">
         <f t="shared" si="0"/>
-        <v>4.8999999999999986</v>
-      </c>
-      <c r="J27">
-        <f>C27-E27</f>
-        <v>3.8999999999999986</v>
+        <v>0.17142857142857171</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>-4.2857142857140929E-2</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="2"/>
+        <v>17.271428571428572</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="3"/>
+        <v>21.05714285714286</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>0.52430555555555503</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28">
-        <v>22.5</v>
+        <v>21.1</v>
       </c>
       <c r="D28">
-        <v>18.600000000000001</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="F28">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H28">
+        <f>D28-F28</f>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I28">
+        <f>C28-E28</f>
+        <v>4.1000000000000014</v>
+      </c>
+      <c r="K28">
         <f t="shared" si="0"/>
-        <v>5.4000000000000021</v>
-      </c>
-      <c r="J28">
-        <f>C28-E28</f>
-        <v>4.3000000000000007</v>
+        <v>7.1428571428570287E-2</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>-4.2857142857140929E-2</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="2"/>
+        <v>17.071428571428569</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="3"/>
+        <v>21.05714285714286</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>0.52777777777777701</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29">
-        <v>22.6</v>
+        <v>21.1</v>
       </c>
       <c r="D29">
-        <v>18.600000000000001</v>
+        <v>17</v>
       </c>
       <c r="E29">
-        <v>18.100000000000001</v>
+        <v>17</v>
       </c>
       <c r="F29">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H29">
+        <f>D29-F29</f>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I29">
+        <f>C29-E29</f>
+        <v>4.1000000000000014</v>
+      </c>
+      <c r="K29">
         <f t="shared" si="0"/>
-        <v>5.4000000000000021</v>
-      </c>
-      <c r="J29">
-        <f>C29-E29</f>
-        <v>4.5</v>
+        <v>7.1428571428570287E-2</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>-4.2857142857140929E-2</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="2"/>
+        <v>17.071428571428569</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="3"/>
+        <v>21.05714285714286</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>0.53125</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30">
-        <v>22.6</v>
+        <v>21</v>
       </c>
       <c r="D30">
-        <v>18.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F30">
-        <v>13.1</v>
+        <v>12.3</v>
+      </c>
+      <c r="H30">
+        <f>D30-F30</f>
+        <v>4.5999999999999979</v>
       </c>
       <c r="I30">
+        <f>C30-E30</f>
+        <v>4.1000000000000014</v>
+      </c>
+      <c r="K30">
         <f t="shared" si="0"/>
-        <v>5.4</v>
-      </c>
-      <c r="J30">
-        <f>C30-E30</f>
-        <v>4.6000000000000014</v>
+        <v>7.142857142856851E-2</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>-4.2857142857140929E-2</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="2"/>
+        <v>16.971428571428568</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="3"/>
+        <v>20.957142857142859</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>0.53472222222222199</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31">
-        <v>22.6</v>
+        <v>21</v>
       </c>
       <c r="D31">
-        <v>18.399999999999999</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E31">
-        <v>18.100000000000001</v>
+        <v>17</v>
       </c>
       <c r="F31">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H31">
+        <f>D31-F31</f>
+        <v>4.4999999999999982</v>
       </c>
       <c r="I31">
+        <f>C31-E31</f>
+        <v>4</v>
+      </c>
+      <c r="K31">
         <f t="shared" si="0"/>
-        <v>5.1999999999999993</v>
-      </c>
-      <c r="J31">
-        <f>C31-E31</f>
-        <v>4.5</v>
+        <v>-2.8571428571431134E-2</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>-0.14285714285714235</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="2"/>
+        <v>16.871428571428567</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="3"/>
+        <v>20.857142857142858</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>0.53819444444444398</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32">
-        <v>22.5</v>
+        <v>20.9</v>
       </c>
       <c r="D32">
-        <v>18.3</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H32">
+        <f>D32-F32</f>
+        <v>4.4999999999999982</v>
       </c>
       <c r="I32">
+        <f>C32-E32</f>
+        <v>3.8999999999999986</v>
+      </c>
+      <c r="K32">
         <f t="shared" si="0"/>
-        <v>5.2000000000000011</v>
-      </c>
-      <c r="J32">
-        <f>C32-E32</f>
-        <v>4.5</v>
+        <v>-2.8571428571431134E-2</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>-0.24285714285714377</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="2"/>
+        <v>16.871428571428567</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="3"/>
+        <v>20.657142857142855</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>0.54166666666666696</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33">
-        <v>22.6</v>
+        <v>20.9</v>
       </c>
       <c r="D33">
-        <v>18.5</v>
+        <v>16.8</v>
       </c>
       <c r="E33">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F33">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H33">
+        <f>D33-F33</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I33">
+        <f>C33-E33</f>
+        <v>3.8999999999999986</v>
+      </c>
+      <c r="K33">
         <f t="shared" si="0"/>
-        <v>5.4</v>
-      </c>
-      <c r="J33">
-        <f>C33-E33</f>
-        <v>4.6000000000000014</v>
+        <v>-0.128571428571429</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>-0.24285714285714377</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="2"/>
+        <v>16.671428571428571</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="3"/>
+        <v>20.657142857142855</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>0.54513888888888895</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="D34">
-        <v>18.2</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="E34">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F34">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H34">
+        <f>D34-F34</f>
+        <v>5.9999999999999982</v>
       </c>
       <c r="I34">
+        <f>C34-E34</f>
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="K34">
         <f t="shared" si="0"/>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="J34">
-        <f>C34-E34</f>
-        <v>4.5</v>
+        <v>1.4714285714285689</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>1.5571428571428569</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="2"/>
+        <v>19.871428571428567</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="3"/>
+        <v>24.257142857142856</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>0.54861111111111105</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35">
-        <v>22.5</v>
+        <v>21.9</v>
       </c>
       <c r="D35">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="E35">
-        <v>17.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="F35">
-        <v>13</v>
+        <v>12.4</v>
+      </c>
+      <c r="H35">
+        <f>D35-F35</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I35">
+        <f>C35-E35</f>
+        <v>4.8999999999999986</v>
+      </c>
+      <c r="K35">
         <f t="shared" si="0"/>
-        <v>5.1999999999999993</v>
-      </c>
-      <c r="J35">
-        <f>C35-E35</f>
-        <v>4.6000000000000014</v>
+        <v>0.371428571428571</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="1"/>
+        <v>0.75714285714285623</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="2"/>
+        <v>17.671428571428571</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="3"/>
+        <v>22.657142857142855</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>0.55208333333333304</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="D36">
-        <v>18.100000000000001</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>17.899999999999999</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F36">
-        <v>13</v>
+        <v>12.3</v>
+      </c>
+      <c r="H36">
+        <f>D36-F36</f>
+        <v>4.6999999999999993</v>
       </c>
       <c r="I36">
+        <f>C36-E36</f>
+        <v>4.7000000000000028</v>
+      </c>
+      <c r="K36">
         <f t="shared" si="0"/>
-        <v>5.1000000000000014</v>
-      </c>
-      <c r="J36">
-        <f>C36-E36</f>
-        <v>4.5</v>
+        <v>0.17142857142856993</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="1"/>
+        <v>0.55714285714286049</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="2"/>
+        <v>17.171428571428571</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="3"/>
+        <v>22.157142857142862</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>0.55555555555555503</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37">
-        <v>22.4</v>
+        <v>21.3</v>
       </c>
       <c r="D37">
-        <v>18.100000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="E37">
-        <v>17.899999999999999</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F37">
-        <v>13</v>
+        <v>12.3</v>
+      </c>
+      <c r="H37">
+        <f>D37-F37</f>
+        <v>4.5</v>
       </c>
       <c r="I37">
+        <f>C37-E37</f>
+        <v>4.4000000000000021</v>
+      </c>
+      <c r="K37">
         <f t="shared" si="0"/>
-        <v>5.1000000000000014</v>
-      </c>
-      <c r="J37">
-        <f>C37-E37</f>
-        <v>4.5</v>
+        <v>-2.8571428571429358E-2</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="1"/>
+        <v>0.25714285714285978</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="2"/>
+        <v>16.771428571428572</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="3"/>
+        <v>21.55714285714286</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>0.55902777777777801</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38">
-        <v>22.4</v>
+        <v>21.2</v>
       </c>
       <c r="D38">
-        <v>18.100000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F38">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H38">
+        <f>D38-F38</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I38">
+        <f>C38-E38</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="K38">
         <f t="shared" si="0"/>
-        <v>5.0000000000000018</v>
-      </c>
-      <c r="J38">
-        <f>C38-E38</f>
-        <v>4.3999999999999986</v>
+        <v>-0.128571428571429</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="1"/>
+        <v>5.714285714285694E-2</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="2"/>
+        <v>16.671428571428571</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="3"/>
+        <v>21.257142857142856</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>0.5625</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39">
-        <v>25.4</v>
+        <v>20.8</v>
       </c>
       <c r="D39">
-        <v>20.9</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="E39">
-        <v>18.399999999999999</v>
+        <v>17</v>
       </c>
       <c r="F39">
-        <v>14.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H39">
+        <f>D39-F39</f>
+        <v>3.9999999999999982</v>
       </c>
       <c r="I39">
+        <f>C39-E39</f>
+        <v>3.8000000000000007</v>
+      </c>
+      <c r="K39">
         <f t="shared" si="0"/>
-        <v>6.7999999999999989</v>
-      </c>
-      <c r="J39">
-        <f>C39-E39</f>
-        <v>7</v>
+        <v>-0.52857142857143113</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="1"/>
+        <v>-0.34285714285714164</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="2"/>
+        <v>15.871428571428567</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="3"/>
+        <v>20.457142857142859</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>0.56597222222222199</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40">
-        <v>26.4</v>
+        <v>20.8</v>
       </c>
       <c r="D40">
-        <v>21.2</v>
+        <v>16.3</v>
       </c>
       <c r="E40">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>15.3</v>
+        <v>12.5</v>
+      </c>
+      <c r="H40">
+        <f>D40-F40</f>
+        <v>3.8000000000000007</v>
       </c>
       <c r="I40">
+        <f>C40-E40</f>
+        <v>3.8000000000000007</v>
+      </c>
+      <c r="K40">
         <f t="shared" si="0"/>
-        <v>5.8999999999999986</v>
-      </c>
-      <c r="J40">
-        <f>C40-E40</f>
-        <v>7.3999999999999986</v>
+        <v>-0.72857142857142865</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="1"/>
+        <v>-0.34285714285714164</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="2"/>
+        <v>15.571428571428573</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="3"/>
+        <v>20.457142857142859</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>0.56944444444444398</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41">
-        <v>27.6</v>
+        <v>20.8</v>
       </c>
       <c r="D41">
-        <v>21.7</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="E41">
-        <v>18.399999999999999</v>
+        <v>17</v>
       </c>
       <c r="F41">
-        <v>14</v>
+        <v>12.4</v>
+      </c>
+      <c r="H41">
+        <f>D41-F41</f>
+        <v>3.9999999999999982</v>
       </c>
       <c r="I41">
+        <f>C41-E41</f>
+        <v>3.8000000000000007</v>
+      </c>
+      <c r="K41">
         <f t="shared" si="0"/>
-        <v>7.6999999999999993</v>
-      </c>
-      <c r="J41">
-        <f>C41-E41</f>
-        <v>9.2000000000000028</v>
+        <v>-0.52857142857143113</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="1"/>
+        <v>-0.34285714285714164</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="2"/>
+        <v>15.871428571428567</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="3"/>
+        <v>20.457142857142859</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>0.57291666666666596</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42">
-        <v>27.8</v>
+        <v>20.7</v>
       </c>
       <c r="D42">
-        <v>21.4</v>
+        <v>16.3</v>
       </c>
       <c r="E42">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="F42">
-        <v>13.5</v>
+        <v>12.4</v>
+      </c>
+      <c r="H42">
+        <f>D42-F42</f>
+        <v>3.9000000000000004</v>
       </c>
       <c r="I42">
+        <f>C42-E42</f>
+        <v>3.6999999999999993</v>
+      </c>
+      <c r="K42">
         <f t="shared" si="0"/>
-        <v>7.8999999999999986</v>
-      </c>
-      <c r="J42">
-        <f>C42-E42</f>
-        <v>9.6000000000000014</v>
+        <v>-0.628571428571429</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="1"/>
+        <v>-0.44285714285714306</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="2"/>
+        <v>15.671428571428571</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="3"/>
+        <v>20.257142857142856</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>0.57638888888888895</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43">
-        <v>29.3</v>
+        <v>20.7</v>
       </c>
       <c r="D43">
-        <v>22.7</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="E43">
-        <v>18.3</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F43">
-        <v>13.6</v>
+        <v>12.3</v>
+      </c>
+      <c r="H43">
+        <f>D43-F43</f>
+        <v>4.0999999999999979</v>
       </c>
       <c r="I43">
+        <f>C43-E43</f>
+        <v>3.8000000000000007</v>
+      </c>
+      <c r="K43">
         <f t="shared" si="0"/>
-        <v>9.1</v>
-      </c>
-      <c r="J43">
-        <f>C43-E43</f>
-        <v>11</v>
+        <v>-0.42857142857143149</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="1"/>
+        <v>-0.34285714285714164</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="2"/>
+        <v>15.971428571428568</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="3"/>
+        <v>20.357142857142858</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>0.57986111111111105</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44">
-        <v>28.2</v>
+        <v>20.8</v>
       </c>
       <c r="D44">
-        <v>21.1</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E44">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="F44">
-        <v>13.4</v>
+        <v>12.4</v>
+      </c>
+      <c r="H44">
+        <f>D44-F44</f>
+        <v>4.2000000000000011</v>
       </c>
       <c r="I44">
+        <f>C44-E44</f>
+        <v>3.8000000000000007</v>
+      </c>
+      <c r="K44">
         <f t="shared" si="0"/>
-        <v>7.7000000000000011</v>
-      </c>
-      <c r="J44">
-        <f>C44-E44</f>
-        <v>10</v>
+        <v>-0.32857142857142829</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="1"/>
+        <v>-0.34285714285714164</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="2"/>
+        <v>16.271428571428572</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="3"/>
+        <v>20.457142857142859</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>0.58333333333333304</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45">
-        <v>26.6</v>
+        <v>21.5</v>
       </c>
       <c r="D45">
-        <v>19.899999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="E45">
-        <v>18.100000000000001</v>
+        <v>17</v>
       </c>
       <c r="F45">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H45">
+        <f>D45-F45</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I45">
+        <f>C45-E45</f>
+        <v>4.5</v>
+      </c>
+      <c r="K45">
         <f t="shared" si="0"/>
-        <v>6.6999999999999993</v>
-      </c>
-      <c r="J45">
-        <f>C45-E45</f>
-        <v>8.5</v>
+        <v>0.371428571428571</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="1"/>
+        <v>0.35714285714285765</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="2"/>
+        <v>17.671428571428571</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="3"/>
+        <v>21.857142857142858</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>0.58680555555555503</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46">
-        <v>29.9</v>
+        <v>22.2</v>
       </c>
       <c r="D46">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E46">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F46">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H46">
+        <f>D46-F46</f>
+        <v>5.4</v>
       </c>
       <c r="I46">
+        <f>C46-E46</f>
+        <v>5.1999999999999993</v>
+      </c>
+      <c r="K46">
         <f t="shared" si="0"/>
-        <v>10.100000000000001</v>
-      </c>
-      <c r="J46">
-        <f>C46-E46</f>
-        <v>11.899999999999999</v>
+        <v>0.871428571428571</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="1"/>
+        <v>1.0571428571428569</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="2"/>
+        <v>18.671428571428571</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="3"/>
+        <v>23.257142857142856</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>0.59027777777777701</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47">
-        <v>29.9</v>
+        <v>22.8</v>
       </c>
       <c r="D47">
-        <v>23</v>
+        <v>18.2</v>
       </c>
       <c r="E47">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F47">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H47">
+        <f>D47-F47</f>
+        <v>5.7999999999999989</v>
       </c>
       <c r="I47">
+        <f>C47-E47</f>
+        <v>5.8000000000000007</v>
+      </c>
+      <c r="K47">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J47">
-        <f>C47-E47</f>
-        <v>11.899999999999999</v>
+        <v>1.2714285714285696</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="1"/>
+        <v>1.6571428571428584</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="2"/>
+        <v>19.471428571428568</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="3"/>
+        <v>24.457142857142859</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>0.59375</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48">
-        <v>30.2</v>
+        <v>22.5</v>
       </c>
       <c r="D48">
-        <v>23</v>
+        <v>17.7</v>
       </c>
       <c r="E48">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F48">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H48">
+        <f>D48-F48</f>
+        <v>5.2999999999999989</v>
       </c>
       <c r="I48">
+        <f>C48-E48</f>
+        <v>5.5</v>
+      </c>
+      <c r="K48">
         <f t="shared" si="0"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J48">
-        <f>C48-E48</f>
-        <v>12.2</v>
+        <v>0.77142857142856958</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="1"/>
+        <v>1.3571428571428577</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="2"/>
+        <v>18.471428571428568</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="3"/>
+        <v>23.857142857142858</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>0.59722222222222199</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49">
-        <v>30.1</v>
+        <v>22.5</v>
       </c>
       <c r="D49">
-        <v>22.8</v>
+        <v>17.8</v>
       </c>
       <c r="E49">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F49">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H49">
+        <f>D49-F49</f>
+        <v>5.4</v>
       </c>
       <c r="I49">
+        <f>C49-E49</f>
+        <v>5.5</v>
+      </c>
+      <c r="K49">
         <f t="shared" si="0"/>
-        <v>9.7000000000000011</v>
-      </c>
-      <c r="J49">
-        <f>C49-E49</f>
-        <v>12.100000000000001</v>
+        <v>0.871428571428571</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="1"/>
+        <v>1.3571428571428577</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="2"/>
+        <v>18.671428571428571</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="3"/>
+        <v>23.857142857142858</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>0.60069444444444398</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50">
-        <v>30.4</v>
+        <v>22.9</v>
       </c>
       <c r="D50">
-        <v>23</v>
+        <v>18.2</v>
       </c>
       <c r="E50">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F50">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H50">
+        <f>D50-F50</f>
+        <v>5.7999999999999989</v>
       </c>
       <c r="I50">
+        <f>C50-E50</f>
+        <v>5.8999999999999986</v>
+      </c>
+      <c r="K50">
         <f t="shared" si="0"/>
-        <v>9.9</v>
-      </c>
-      <c r="J50">
-        <f>C50-E50</f>
-        <v>12.399999999999999</v>
+        <v>1.2714285714285696</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="1"/>
+        <v>1.7571428571428562</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="2"/>
+        <v>19.471428571428568</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="3"/>
+        <v>24.657142857142855</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>0.60416666666666596</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51">
-        <v>30.4</v>
+        <v>22.6</v>
       </c>
       <c r="D51">
-        <v>22.7</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F51">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H51">
+        <f>D51-F51</f>
+        <v>5.4999999999999982</v>
       </c>
       <c r="I51">
+        <f>C51-E51</f>
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="K51">
         <f t="shared" si="0"/>
-        <v>9.6</v>
-      </c>
-      <c r="J51">
-        <f>C51-E51</f>
-        <v>12.399999999999999</v>
+        <v>0.97142857142856887</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="1"/>
+        <v>1.4571428571428591</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="2"/>
+        <v>18.871428571428567</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="3"/>
+        <v>24.05714285714286</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>0.60763888888888795</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52">
-        <v>27.6</v>
+        <v>22.3</v>
       </c>
       <c r="D52">
-        <v>20.8</v>
+        <v>17.5</v>
       </c>
       <c r="E52">
-        <v>18</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F52">
-        <v>13.1</v>
+        <v>12.3</v>
+      </c>
+      <c r="H52">
+        <f>D52-F52</f>
+        <v>5.1999999999999993</v>
       </c>
       <c r="I52">
+        <f>C52-E52</f>
+        <v>5.4000000000000021</v>
+      </c>
+      <c r="K52">
         <f t="shared" si="0"/>
-        <v>7.7000000000000011</v>
-      </c>
-      <c r="J52">
-        <f>C52-E52</f>
-        <v>9.6000000000000014</v>
+        <v>0.67142857142856993</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="1"/>
+        <v>1.2571428571428598</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="2"/>
+        <v>18.171428571428571</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="3"/>
+        <v>23.55714285714286</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>0.61111111111111105</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53">
-        <v>26.8</v>
+        <v>22.4</v>
       </c>
       <c r="D53">
-        <v>20.6</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E53">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53">
-        <v>13.1</v>
+        <v>12.2</v>
+      </c>
+      <c r="H53">
+        <f>D53-F53</f>
+        <v>5.6999999999999993</v>
       </c>
       <c r="I53">
+        <f>C53-E53</f>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="K53">
         <f t="shared" si="0"/>
-        <v>7.5000000000000018</v>
-      </c>
-      <c r="J53">
-        <f>C53-E53</f>
-        <v>8.8000000000000007</v>
+        <v>1.1714285714285699</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="1"/>
+        <v>1.2571428571428562</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="2"/>
+        <v>19.071428571428569</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="3"/>
+        <v>23.657142857142855</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>0.61458333333333304</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54">
-        <v>28</v>
+        <v>23.2</v>
       </c>
       <c r="D54">
-        <v>21.7</v>
+        <v>18.7</v>
       </c>
       <c r="E54">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F54">
-        <v>13</v>
+        <v>12.2</v>
+      </c>
+      <c r="H54">
+        <f>D54-F54</f>
+        <v>6.5</v>
       </c>
       <c r="I54">
+        <f>C54-E54</f>
+        <v>6.1999999999999993</v>
+      </c>
+      <c r="K54">
         <f t="shared" si="0"/>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="J54">
-        <f>C54-E54</f>
-        <v>10</v>
+        <v>1.9714285714285706</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="1"/>
+        <v>2.0571428571428569</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="2"/>
+        <v>20.671428571428571</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="3"/>
+        <v>25.257142857142856</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>0.61805555555555503</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55">
-        <v>30.2</v>
+        <v>23.3</v>
       </c>
       <c r="D55">
-        <v>23.3</v>
+        <v>18.8</v>
       </c>
       <c r="E55">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F55">
-        <v>13</v>
+        <v>12.3</v>
+      </c>
+      <c r="H55">
+        <f>D55-F55</f>
+        <v>6.5</v>
       </c>
       <c r="I55">
+        <f>C55-E55</f>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="K55">
         <f t="shared" si="0"/>
-        <v>10.3</v>
-      </c>
-      <c r="J55">
-        <f>C55-E55</f>
-        <v>12.2</v>
+        <v>1.9714285714285706</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="1"/>
+        <v>2.1571428571428584</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="2"/>
+        <v>20.771428571428572</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="3"/>
+        <v>25.457142857142859</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>0.62152777777777701</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56">
-        <v>28.1</v>
+        <v>23</v>
       </c>
       <c r="D56">
-        <v>21.2</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="E56">
-        <v>17.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="F56">
-        <v>13</v>
+        <v>12.3</v>
+      </c>
+      <c r="H56">
+        <f>D56-F56</f>
+        <v>5.8000000000000007</v>
       </c>
       <c r="I56">
+        <f>C56-E56</f>
+        <v>6</v>
+      </c>
+      <c r="K56">
         <f t="shared" si="0"/>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="J56">
-        <f>C56-E56</f>
-        <v>10.200000000000003</v>
+        <v>1.2714285714285714</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="1"/>
+        <v>1.8571428571428577</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="2"/>
+        <v>19.371428571428574</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="3"/>
+        <v>24.857142857142858</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>0.625</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57">
-        <v>26.1</v>
+        <v>22.6</v>
       </c>
       <c r="D57">
-        <v>19.899999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="E57">
-        <v>18.100000000000001</v>
+        <v>17</v>
       </c>
       <c r="F57">
-        <v>13.3</v>
+        <v>12.4</v>
+      </c>
+      <c r="H57">
+        <f>D57-F57</f>
+        <v>5.2999999999999989</v>
       </c>
       <c r="I57">
+        <f>C57-E57</f>
+        <v>5.6000000000000014</v>
+      </c>
+      <c r="K57">
         <f t="shared" si="0"/>
-        <v>6.5999999999999979</v>
-      </c>
-      <c r="J57">
-        <f>C57-E57</f>
-        <v>8</v>
+        <v>0.77142857142856958</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="1"/>
+        <v>1.4571428571428591</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="2"/>
+        <v>18.471428571428568</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="3"/>
+        <v>24.05714285714286</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>0.62847222222222199</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58">
-        <v>24.4</v>
+        <v>21.9</v>
       </c>
       <c r="D58">
-        <v>18.8</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="E58">
-        <v>17.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="F58">
-        <v>12.9</v>
+        <v>12.4</v>
+      </c>
+      <c r="H58">
+        <f>D58-F58</f>
+        <v>4.7000000000000011</v>
       </c>
       <c r="I58">
+        <f>C58-E58</f>
+        <v>4.8999999999999986</v>
+      </c>
+      <c r="K58">
         <f t="shared" si="0"/>
-        <v>5.9</v>
-      </c>
-      <c r="J58">
-        <f>C58-E58</f>
-        <v>6.5</v>
+        <v>0.17142857142857171</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="1"/>
+        <v>0.75714285714285623</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="2"/>
+        <v>17.271428571428572</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="3"/>
+        <v>22.657142857142855</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>0.63194444444444398</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59">
-        <v>26.4</v>
+        <v>22</v>
       </c>
       <c r="D59">
-        <v>21</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="E59">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F59">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H59">
+        <f>D59-F59</f>
+        <v>4.9999999999999982</v>
       </c>
       <c r="I59">
+        <f>C59-E59</f>
+        <v>5</v>
+      </c>
+      <c r="K59">
         <f t="shared" si="0"/>
-        <v>7.8000000000000007</v>
-      </c>
-      <c r="J59">
-        <f>C59-E59</f>
-        <v>8.3999999999999986</v>
+        <v>0.47142857142856887</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="1"/>
+        <v>0.85714285714285765</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="2"/>
+        <v>17.871428571428567</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="3"/>
+        <v>22.857142857142858</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>0.63541666666666596</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60">
-        <v>28.4</v>
+        <v>22.7</v>
       </c>
       <c r="D60">
-        <v>22.5</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="E60">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F60">
-        <v>13.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="H60">
+        <f>D60-F60</f>
+        <v>5.6000000000000014</v>
       </c>
       <c r="I60">
+        <f>C60-E60</f>
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="K60">
         <f t="shared" si="0"/>
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="J60">
-        <f>C60-E60</f>
-        <v>10.399999999999999</v>
+        <v>1.0714285714285721</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="1"/>
+        <v>1.5571428571428569</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="2"/>
+        <v>19.171428571428574</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="3"/>
+        <v>24.257142857142856</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>0.63888888888888795</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61">
-        <v>29.1</v>
+        <v>22.4</v>
       </c>
       <c r="D61">
-        <v>22.6</v>
+        <v>17.7</v>
       </c>
       <c r="E61">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F61">
-        <v>13.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="H61">
+        <f>D61-F61</f>
+        <v>5.1999999999999993</v>
       </c>
       <c r="I61">
+        <f>C61-E61</f>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="K61">
         <f t="shared" si="0"/>
-        <v>9.4000000000000021</v>
-      </c>
-      <c r="J61">
-        <f>C61-E61</f>
-        <v>11.100000000000001</v>
+        <v>0.67142857142856993</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="1"/>
+        <v>1.2571428571428562</v>
+      </c>
+      <c r="N61">
+        <f t="shared" si="2"/>
+        <v>18.37142857142857</v>
+      </c>
+      <c r="O61">
+        <f t="shared" si="3"/>
+        <v>23.657142857142855</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>0.64236111111111105</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62">
-        <v>27.1</v>
+        <v>22.2</v>
       </c>
       <c r="D62">
-        <v>20.6</v>
+        <v>17.5</v>
       </c>
       <c r="E62">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F62">
-        <v>13.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="H62">
+        <f>D62-F62</f>
+        <v>5</v>
       </c>
       <c r="I62">
+        <f>C62-E62</f>
+        <v>5.1999999999999993</v>
+      </c>
+      <c r="K62">
         <f t="shared" si="0"/>
-        <v>7.4000000000000021</v>
-      </c>
-      <c r="J62">
-        <f>C62-E62</f>
-        <v>9.1000000000000014</v>
+        <v>0.47142857142857064</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="1"/>
+        <v>1.0571428571428569</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="2"/>
+        <v>17.971428571428572</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="3"/>
+        <v>23.257142857142856</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>0.64583333333333304</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63">
-        <v>26.1</v>
+        <v>22.1</v>
       </c>
       <c r="D63">
-        <v>20.3</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E63">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F63">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H63">
+        <f>D63-F63</f>
+        <v>5.2000000000000011</v>
       </c>
       <c r="I63">
+        <f>C63-E63</f>
+        <v>5.1000000000000014</v>
+      </c>
+      <c r="K63">
         <f t="shared" si="0"/>
-        <v>7.1000000000000014</v>
-      </c>
-      <c r="J63">
-        <f>C63-E63</f>
-        <v>8.1000000000000014</v>
+        <v>0.67142857142857171</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="1"/>
+        <v>0.95714285714285907</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="2"/>
+        <v>18.271428571428572</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="3"/>
+        <v>23.05714285714286</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>0.64930555555555503</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64">
-        <v>28.1</v>
+        <v>22.5</v>
       </c>
       <c r="D64">
-        <v>21.9</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="E64">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F64">
-        <v>13.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="H64">
+        <f>D64-F64</f>
+        <v>5.6000000000000014</v>
       </c>
       <c r="I64">
+        <f>C64-E64</f>
+        <v>5.5</v>
+      </c>
+      <c r="K64">
         <f t="shared" si="0"/>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="J64">
-        <f>C64-E64</f>
-        <v>10.100000000000001</v>
+        <v>1.0714285714285721</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="1"/>
+        <v>1.3571428571428577</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="2"/>
+        <v>19.171428571428574</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="3"/>
+        <v>23.857142857142858</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>0.65277777777777701</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65">
-        <v>28.9</v>
+        <v>22.8</v>
       </c>
       <c r="D65">
-        <v>22.2</v>
+        <v>18.3</v>
       </c>
       <c r="E65">
-        <v>18</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="F65">
-        <v>13.1</v>
+        <v>12.5</v>
+      </c>
+      <c r="H65">
+        <f>D65-F65</f>
+        <v>5.8000000000000007</v>
       </c>
       <c r="I65">
+        <f>C65-E65</f>
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="K65">
         <f t="shared" si="0"/>
-        <v>9.1</v>
-      </c>
-      <c r="J65">
-        <f>C65-E65</f>
-        <v>10.899999999999999</v>
+        <v>1.2714285714285714</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="1"/>
+        <v>1.5571428571428569</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="2"/>
+        <v>19.571428571428573</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="3"/>
+        <v>24.357142857142858</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>0.656249999999999</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66">
-        <v>32.1</v>
+        <v>22.4</v>
       </c>
       <c r="D66">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E66">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F66">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H66">
+        <f>D66-F66</f>
+        <v>5.4</v>
       </c>
       <c r="I66">
+        <f>C66-E66</f>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="K66">
         <f t="shared" si="0"/>
-        <v>10.100000000000001</v>
-      </c>
-      <c r="J66">
-        <f>C66-E66</f>
-        <v>14.100000000000001</v>
+        <v>0.871428571428571</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="1"/>
+        <v>1.2571428571428562</v>
+      </c>
+      <c r="N66">
+        <f t="shared" si="2"/>
+        <v>18.671428571428571</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="3"/>
+        <v>23.657142857142855</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>0.65972222222222199</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67">
-        <v>30.3</v>
+        <v>22.2</v>
       </c>
       <c r="D67">
-        <v>21.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E67">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F67">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H67">
+        <f>D67-F67</f>
+        <v>5.2000000000000011</v>
       </c>
       <c r="I67">
-        <f t="shared" ref="I67:I77" si="1">D67-F67</f>
-        <v>8.5000000000000018</v>
-      </c>
-      <c r="J67">
         <f>C67-E67</f>
-        <v>12.3</v>
+        <v>5.1999999999999993</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K77" si="4">H67-H$80</f>
+        <v>0.67142857142857171</v>
+      </c>
+      <c r="L67">
+        <f t="shared" ref="L67:L77" si="5">I67-I$80</f>
+        <v>1.0571428571428569</v>
+      </c>
+      <c r="N67">
+        <f t="shared" ref="N67:N77" si="6">D67+K67</f>
+        <v>18.271428571428572</v>
+      </c>
+      <c r="O67">
+        <f t="shared" ref="O67:O77" si="7">C67+L67</f>
+        <v>23.257142857142856</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>0.66319444444444398</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68">
-        <v>29.3</v>
+        <v>21.8</v>
       </c>
       <c r="D68">
-        <v>21</v>
+        <v>17.3</v>
       </c>
       <c r="E68">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F68">
-        <v>13.2</v>
+        <v>12.4</v>
+      </c>
+      <c r="H68">
+        <f>D68-F68</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I68">
-        <f t="shared" si="1"/>
-        <v>7.8000000000000007</v>
-      </c>
-      <c r="J68">
         <f>C68-E68</f>
-        <v>11.3</v>
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="4"/>
+        <v>0.371428571428571</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="5"/>
+        <v>0.65714285714285836</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="6"/>
+        <v>17.671428571428571</v>
+      </c>
+      <c r="O68">
+        <f t="shared" si="7"/>
+        <v>22.457142857142859</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>0.66666666666666596</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69">
-        <v>28.9</v>
+        <v>21.6</v>
       </c>
       <c r="D69">
-        <v>21.2</v>
+        <v>17.2</v>
       </c>
       <c r="E69">
-        <v>18</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="F69">
-        <v>13.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="H69">
+        <f>D69-F69</f>
+        <v>4.6999999999999993</v>
       </c>
       <c r="I69">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="J69">
         <f>C69-E69</f>
-        <v>10.899999999999999</v>
+        <v>4.5</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="4"/>
+        <v>0.17142857142856993</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="5"/>
+        <v>0.35714285714285765</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="6"/>
+        <v>17.37142857142857</v>
+      </c>
+      <c r="O69">
+        <f t="shared" si="7"/>
+        <v>21.957142857142859</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>0.67013888888888795</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70">
-        <v>27.9</v>
+        <v>22</v>
       </c>
       <c r="D70">
-        <v>20.7</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E70">
-        <v>18</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="F70">
-        <v>13.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="H70">
+        <f>D70-F70</f>
+        <v>5.1000000000000014</v>
       </c>
       <c r="I70">
-        <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-      <c r="J70">
         <f>C70-E70</f>
-        <v>9.8999999999999986</v>
+        <v>4.8999999999999986</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="4"/>
+        <v>0.57142857142857206</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="5"/>
+        <v>0.75714285714285623</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="6"/>
+        <v>18.171428571428574</v>
+      </c>
+      <c r="O70">
+        <f t="shared" si="7"/>
+        <v>22.757142857142856</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>0.67361111111111005</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71">
-        <v>28</v>
+        <v>21.9</v>
       </c>
       <c r="D71">
-        <v>21.2</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="E71">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F71">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H71">
+        <f>D71-F71</f>
+        <v>4.7000000000000011</v>
       </c>
       <c r="I71">
-        <f t="shared" si="1"/>
-        <v>8.1</v>
-      </c>
-      <c r="J71">
         <f>C71-E71</f>
-        <v>10</v>
+        <v>4.8999999999999986</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="4"/>
+        <v>0.17142857142857171</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="5"/>
+        <v>0.75714285714285623</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="6"/>
+        <v>17.271428571428572</v>
+      </c>
+      <c r="O71">
+        <f t="shared" si="7"/>
+        <v>22.657142857142855</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>0.67708333333333304</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72">
-        <v>27.2</v>
+        <v>22</v>
       </c>
       <c r="D72">
-        <v>20.6</v>
+        <v>17.3</v>
       </c>
       <c r="E72">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F72">
-        <v>13.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="H72">
+        <f>D72-F72</f>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I72">
-        <f t="shared" si="1"/>
-        <v>7.5000000000000018</v>
-      </c>
-      <c r="J72">
         <f>C72-E72</f>
-        <v>9.1999999999999993</v>
+        <v>5</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="4"/>
+        <v>0.371428571428571</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="5"/>
+        <v>0.85714285714285765</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="6"/>
+        <v>17.671428571428571</v>
+      </c>
+      <c r="O72">
+        <f t="shared" si="7"/>
+        <v>22.857142857142858</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>0.68055555555555503</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73">
-        <v>25.4</v>
+        <v>22.4</v>
       </c>
       <c r="D73">
-        <v>19.5</v>
+        <v>17.8</v>
       </c>
       <c r="E73">
-        <v>17.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="F73">
-        <v>13</v>
+        <v>12.4</v>
+      </c>
+      <c r="H73">
+        <f>D73-F73</f>
+        <v>5.4</v>
       </c>
       <c r="I73">
-        <f t="shared" si="1"/>
-        <v>6.5</v>
-      </c>
-      <c r="J73">
         <f>C73-E73</f>
-        <v>7.5</v>
+        <v>5.3999999999999986</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="4"/>
+        <v>0.871428571428571</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="5"/>
+        <v>1.2571428571428562</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="6"/>
+        <v>18.671428571428571</v>
+      </c>
+      <c r="O73">
+        <f t="shared" si="7"/>
+        <v>23.657142857142855</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>0.68402777777777701</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74">
-        <v>24.3</v>
+        <v>22.3</v>
       </c>
       <c r="D74">
-        <v>18.8</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E74">
         <v>18</v>
       </c>
       <c r="F74">
-        <v>13.1</v>
+        <v>14.5</v>
+      </c>
+      <c r="H74">
+        <f>D74-F74</f>
+        <v>3.3999999999999986</v>
       </c>
       <c r="I74">
-        <f t="shared" si="1"/>
-        <v>5.7000000000000011</v>
-      </c>
-      <c r="J74">
         <f>C74-E74</f>
-        <v>6.3000000000000007</v>
+        <v>4.3000000000000007</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="4"/>
+        <v>-1.1285714285714308</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="5"/>
+        <v>0.15714285714285836</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="6"/>
+        <v>16.771428571428569</v>
+      </c>
+      <c r="O74">
+        <f t="shared" si="7"/>
+        <v>22.457142857142859</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>0.687499999999999</v>
       </c>
       <c r="B75" s="1"/>
       <c r="C75">
-        <v>24.4</v>
+        <v>22.3</v>
       </c>
       <c r="D75">
-        <v>18.899999999999999</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="E75">
-        <v>18</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="F75">
-        <v>13.1</v>
+        <v>17.5</v>
+      </c>
+      <c r="H75">
+        <f>D75-F75</f>
+        <v>0.39999999999999858</v>
       </c>
       <c r="I75">
-        <f t="shared" si="1"/>
-        <v>5.7999999999999989</v>
-      </c>
-      <c r="J75">
         <f>C75-E75</f>
-        <v>6.3999999999999986</v>
+        <v>2.1999999999999993</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="4"/>
+        <v>-4.1285714285714308</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="5"/>
+        <v>-1.9428571428571431</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="6"/>
+        <v>13.771428571428569</v>
+      </c>
+      <c r="O75">
+        <f t="shared" si="7"/>
+        <v>20.357142857142858</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>0.69097222222222199</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76">
-        <v>24.2</v>
+        <v>22.3</v>
       </c>
       <c r="D76">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="E76">
-        <v>18.899999999999999</v>
+        <v>21.3</v>
       </c>
       <c r="F76">
-        <v>15.5</v>
+        <v>17.2</v>
+      </c>
+      <c r="H76">
+        <f>D76-F76</f>
+        <v>0.60000000000000142</v>
       </c>
       <c r="I76">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000007</v>
-      </c>
-      <c r="J76">
         <f>C76-E76</f>
-        <v>5.3000000000000007</v>
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="4"/>
+        <v>-3.9285714285714279</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="5"/>
+        <v>-3.1428571428571423</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="6"/>
+        <v>13.871428571428574</v>
+      </c>
+      <c r="O76">
+        <f t="shared" si="7"/>
+        <v>19.157142857142858</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>0.69444444444444398</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77">
-        <v>24.5</v>
+        <v>22.2</v>
       </c>
       <c r="D77">
-        <v>19</v>
+        <v>17.8</v>
       </c>
       <c r="E77">
-        <v>19.899999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="F77">
-        <v>16.8</v>
+        <v>17.2</v>
+      </c>
+      <c r="H77">
+        <f>D77-F77</f>
+        <v>0.60000000000000142</v>
       </c>
       <c r="I77">
-        <f t="shared" si="1"/>
-        <v>2.1999999999999993</v>
-      </c>
-      <c r="J77">
         <f>C77-E77</f>
-        <v>4.6000000000000014</v>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="4"/>
+        <v>-3.9285714285714279</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="5"/>
+        <v>-3.7428571428571438</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="6"/>
+        <v>13.871428571428574</v>
+      </c>
+      <c r="O77">
+        <f t="shared" si="7"/>
+        <v>18.457142857142856</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G80" t="s">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <f>AVERAGE(H24:H44)</f>
+        <v>4.5285714285714294</v>
+      </c>
+      <c r="I80">
+        <f>AVERAGE(I24:I44)</f>
+        <v>4.1428571428571423</v>
       </c>
     </row>
   </sheetData>
